--- a/doc/Prog.3 - Plantilla planificación (1).xlsx
+++ b/doc/Prog.3 - Plantilla planificación (1).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://deusto-my.sharepoint.com/personal/julen_anda_opendeusto_es/Documents/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://deusto-my.sharepoint.com/personal/julen_anda_opendeusto_es/Documents/Documentos/GitHub/prog3-2025/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BC51B8C17582C56A181AEF2DC7078189EFDD77A0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E85FA8C9-6B22-4015-9196-B72820DF0711}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_BC51B8C17582C56A181AEF2DC7078189EFDD77A0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50D8A76D-9A64-437C-A163-9865F9F40FF9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gantt" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
   <si>
     <t>SEMANA</t>
   </si>
@@ -187,7 +187,7 @@
       <name val="Spectral"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -206,8 +206,14 @@
         <bgColor theme="7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -267,11 +273,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -314,9 +350,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -336,6 +369,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -369,6 +411,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -590,37 +636,37 @@
     <row r="1" spans="1:23" ht="15.75" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="24"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="23"/>
       <c r="T1" s="3"/>
-      <c r="U1" s="25" t="s">
+      <c r="U1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="V1" s="23"/>
-      <c r="W1" s="24"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="23"/>
     </row>
     <row r="2" spans="1:23" ht="27.6">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="24"/>
+      <c r="B2" s="23"/>
       <c r="C2" s="4">
         <v>45565</v>
       </c>
@@ -26085,7 +26131,7 @@
     <col min="2" max="19" width="9.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" customHeight="1">
+    <row r="1" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A1" s="4" t="s">
         <v>26</v>
       </c>
@@ -26161,863 +26207,600 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A2" s="8" t="str">
-        <f>Gantt!A3</f>
-        <v>T1</v>
-      </c>
-      <c r="B2" s="18">
+    <row r="2" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A2" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="27">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!C2+'Julen Anda Gómez'!C2+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D2" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!D2+'Julen Anda Gómez'!D2+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E2" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!E2+'Julen Anda Gómez'!E2+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F2" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!F2+'Julen Anda Gómez'!F2+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G2" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!G2+'Julen Anda Gómez'!G2+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H2" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!H2+'Julen Anda Gómez'!H2+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I2" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!I2+'Julen Anda Gómez'!I2+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J2" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!J2+'Julen Anda Gómez'!J2+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K2" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!K2+'Julen Anda Gómez'!K2+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L2" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!L2+'Julen Anda Gómez'!L2+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M2" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!M2+'Julen Anda Gómez'!M2+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N2" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!N2+'Julen Anda Gómez'!N2+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O2" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!O2+'Julen Anda Gómez'!O2+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="P2" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!P2+'Julen Anda Gómez'!P2+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Q2" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!Q2+'Julen Anda Gómez'!Q2+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="R2" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!R2+'Julen Anda Gómez'!R2+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="S2" s="5" t="e">
-        <f t="shared" ref="S2:S12" si="1">SUM(B2:R2)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A3" s="8" t="str">
-        <f>Gantt!A4</f>
-        <v>T2</v>
-      </c>
-      <c r="B3" s="18">
+      <c r="C2" s="27">
+        <v>10</v>
+      </c>
+      <c r="D2" s="27">
+        <v>10</v>
+      </c>
+      <c r="E2" s="27">
+        <v>7</v>
+      </c>
+      <c r="F2" s="27">
+        <v>5</v>
+      </c>
+      <c r="G2" s="27">
+        <v>7</v>
+      </c>
+      <c r="H2" s="27">
+        <v>1</v>
+      </c>
+      <c r="I2" s="27">
         <v>0</v>
       </c>
-      <c r="C3" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!C3+'Julen Anda Gómez'!C3+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D3" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!D3+'Julen Anda Gómez'!D3+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E3" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!E3+'Julen Anda Gómez'!E3+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F3" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!F3+'Julen Anda Gómez'!F3+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G3" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!G3+'Julen Anda Gómez'!G3+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H3" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!H3+'Julen Anda Gómez'!H3+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I3" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!I3+'Julen Anda Gómez'!I3+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J3" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!J3+'Julen Anda Gómez'!J3+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K3" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!K3+'Julen Anda Gómez'!K3+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L3" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!L3+'Julen Anda Gómez'!L3+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M3" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!M3+'Julen Anda Gómez'!M3+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N3" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!N3+'Julen Anda Gómez'!N3+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O3" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!O3+'Julen Anda Gómez'!O3+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="P3" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!P3+'Julen Anda Gómez'!P3+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Q3" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!Q3+'Julen Anda Gómez'!Q3+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="R3" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!R3+'Julen Anda Gómez'!R3+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="S3" s="5" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A4" s="8" t="str">
-        <f>Gantt!A5</f>
-        <v>T3</v>
-      </c>
-      <c r="B4" s="18">
+      <c r="J2" s="27">
+        <v>1</v>
+      </c>
+      <c r="K2" s="27">
+        <v>1</v>
+      </c>
+      <c r="L2" s="27">
+        <v>2</v>
+      </c>
+      <c r="M2" s="27">
         <v>0</v>
       </c>
-      <c r="C4" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!C4+'Julen Anda Gómez'!C4+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D4" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!D4+'Julen Anda Gómez'!D4+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E4" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!E4+'Julen Anda Gómez'!E4+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F4" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!F4+'Julen Anda Gómez'!F4+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G4" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!G4+'Julen Anda Gómez'!G4+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H4" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!H4+'Julen Anda Gómez'!H4+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I4" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!I4+'Julen Anda Gómez'!I4+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J4" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!J4+'Julen Anda Gómez'!J4+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K4" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!K4+'Julen Anda Gómez'!K4+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L4" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!L4+'Julen Anda Gómez'!L4+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M4" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!M4+'Julen Anda Gómez'!M4+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N4" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!N4+'Julen Anda Gómez'!N4+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O4" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!O4+'Julen Anda Gómez'!O4+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="P4" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!P4+'Julen Anda Gómez'!P4+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Q4" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!Q4+'Julen Anda Gómez'!Q4+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="R4" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!R4+'Julen Anda Gómez'!R4+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="S4" s="5" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A5" s="8" t="str">
-        <f>Gantt!A6</f>
-        <v>T4</v>
-      </c>
-      <c r="B5" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!B5+'Julen Anda Gómez'!B5+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C5" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!C5+'Julen Anda Gómez'!C5+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D5" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!D5+'Julen Anda Gómez'!D5+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E5" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!E5+'Julen Anda Gómez'!E5+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F5" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!F5+'Julen Anda Gómez'!F5+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G5" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!G5+'Julen Anda Gómez'!G5+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H5" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!H5+'Julen Anda Gómez'!H5+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I5" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!I5+'Julen Anda Gómez'!I5+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J5" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!J5+'Julen Anda Gómez'!J5+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K5" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!K5+'Julen Anda Gómez'!K5+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L5" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!L5+'Julen Anda Gómez'!L5+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M5" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!M5+'Julen Anda Gómez'!M5+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N5" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!N5+'Julen Anda Gómez'!N5+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O5" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!O5+'Julen Anda Gómez'!O5+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="P5" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!P5+'Julen Anda Gómez'!P5+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Q5" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!Q5+'Julen Anda Gómez'!Q5+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="R5" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!R5+'Julen Anda Gómez'!R5+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="S5" s="5" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A6" s="8" t="str">
-        <f>Gantt!A7</f>
-        <v>T5</v>
-      </c>
-      <c r="B6" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!B6+'Julen Anda Gómez'!B6+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C6" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!C6+'Julen Anda Gómez'!C6+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D6" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!D6+'Julen Anda Gómez'!D6+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E6" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!E6+'Julen Anda Gómez'!E6+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F6" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!F6+'Julen Anda Gómez'!F6+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G6" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!G6+'Julen Anda Gómez'!G6+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H6" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!H6+'Julen Anda Gómez'!H6+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I6" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!I6+'Julen Anda Gómez'!I6+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J6" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!J6+'Julen Anda Gómez'!J6+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K6" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!K6+'Julen Anda Gómez'!K6+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L6" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!L6+'Julen Anda Gómez'!L6+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M6" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!M6+'Julen Anda Gómez'!M6+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N6" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!N6+'Julen Anda Gómez'!N6+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O6" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!O6+'Julen Anda Gómez'!O6+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="P6" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!P6+'Julen Anda Gómez'!P6+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Q6" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!Q6+'Julen Anda Gómez'!Q6+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="R6" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!R6+'Julen Anda Gómez'!R6+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="S6" s="5" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A7" s="8" t="str">
-        <f>Gantt!A8</f>
-        <v>T6</v>
-      </c>
-      <c r="B7" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!B7+'Julen Anda Gómez'!B7+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C7" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!C7+'Julen Anda Gómez'!C7+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D7" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!D7+'Julen Anda Gómez'!D7+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E7" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!E7+'Julen Anda Gómez'!E7+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F7" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!F7+'Julen Anda Gómez'!F7+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G7" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!G7+'Julen Anda Gómez'!G7+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H7" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!H7+'Julen Anda Gómez'!H7+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I7" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!I7+'Julen Anda Gómez'!I7+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J7" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!J7+'Julen Anda Gómez'!J7+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K7" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!K7+'Julen Anda Gómez'!K7+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L7" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!L7+'Julen Anda Gómez'!L7+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M7" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!M7+'Julen Anda Gómez'!M7+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N7" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!N7+'Julen Anda Gómez'!N7+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O7" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!O7+'Julen Anda Gómez'!O7+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="P7" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!P7+'Julen Anda Gómez'!P7+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Q7" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!Q7+'Julen Anda Gómez'!Q7+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="R7" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!R7+'Julen Anda Gómez'!R7+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="S7" s="5" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A8" s="8" t="str">
-        <f>Gantt!A9</f>
-        <v>T7</v>
-      </c>
-      <c r="B8" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!B8+'Julen Anda Gómez'!B8+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C8" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!C8+'Julen Anda Gómez'!C8+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D8" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!D8+'Julen Anda Gómez'!D8+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E8" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!E8+'Julen Anda Gómez'!E8+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F8" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!F8+'Julen Anda Gómez'!F8+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G8" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!G8+'Julen Anda Gómez'!G8+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H8" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!H8+'Julen Anda Gómez'!H8+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I8" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!I8+'Julen Anda Gómez'!I8+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J8" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!J8+'Julen Anda Gómez'!J8+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K8" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!K8+'Julen Anda Gómez'!K8+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L8" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!L8+'Julen Anda Gómez'!L8+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M8" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!M8+'Julen Anda Gómez'!M8+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N8" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!N8+'Julen Anda Gómez'!N8+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O8" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!O8+'Julen Anda Gómez'!O8+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="P8" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!P8+'Julen Anda Gómez'!P8+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Q8" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!Q8+'Julen Anda Gómez'!Q8+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="R8" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!R8+'Julen Anda Gómez'!R8+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="S8" s="5" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A9" s="8" t="str">
-        <f>Gantt!A10</f>
-        <v>T8</v>
-      </c>
-      <c r="B9" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!B9+'Julen Anda Gómez'!B9+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C9" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!C9+'Julen Anda Gómez'!C9+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D9" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!D9+'Julen Anda Gómez'!D9+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E9" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!E9+'Julen Anda Gómez'!E9+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F9" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!F9+'Julen Anda Gómez'!F9+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G9" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!G9+'Julen Anda Gómez'!G9+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H9" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!H9+'Julen Anda Gómez'!H9+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I9" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!I9+'Julen Anda Gómez'!I9+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J9" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!J9+'Julen Anda Gómez'!J9+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K9" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!K9+'Julen Anda Gómez'!K9+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L9" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!L9+'Julen Anda Gómez'!L9+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M9" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!M9+'Julen Anda Gómez'!M9+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N9" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!N9+'Julen Anda Gómez'!N9+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O9" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!O9+'Julen Anda Gómez'!O9+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="P9" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!P9+'Julen Anda Gómez'!P9+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Q9" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!Q9+'Julen Anda Gómez'!Q9+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="R9" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!R9+'Julen Anda Gómez'!R9+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="S9" s="5" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A10" s="8" t="str">
-        <f>Gantt!A11</f>
-        <v>T9</v>
-      </c>
-      <c r="B10" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!B10+'Julen Anda Gómez'!B10+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C10" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!C10+'Julen Anda Gómez'!C10+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D10" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!D10+'Julen Anda Gómez'!D10+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E10" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!E10+'Julen Anda Gómez'!E10+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F10" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!F10+'Julen Anda Gómez'!F10+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G10" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!G10+'Julen Anda Gómez'!G10+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H10" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!H10+'Julen Anda Gómez'!H10+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I10" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!I10+'Julen Anda Gómez'!I10+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J10" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!J10+'Julen Anda Gómez'!J10+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K10" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!K10+'Julen Anda Gómez'!K10+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L10" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!L10+'Julen Anda Gómez'!L10+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M10" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!M10+'Julen Anda Gómez'!M10+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N10" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!N10+'Julen Anda Gómez'!N10+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O10" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!O10+'Julen Anda Gómez'!O10+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="P10" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!P10+'Julen Anda Gómez'!P10+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Q10" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!Q10+'Julen Anda Gómez'!Q10+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="R10" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!R10+'Julen Anda Gómez'!R10+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="S10" s="5" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A11" s="8" t="str">
-        <f>Gantt!A12</f>
-        <v>T10</v>
-      </c>
-      <c r="B11" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!B11+'Julen Anda Gómez'!B11+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C11" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!C11+'Julen Anda Gómez'!C11+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D11" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!D11+'Julen Anda Gómez'!D11+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E11" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!E11+'Julen Anda Gómez'!E11+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F11" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!F11+'Julen Anda Gómez'!F11+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G11" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!G11+'Julen Anda Gómez'!G11+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H11" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!H11+'Julen Anda Gómez'!H11+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I11" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!I11+'Julen Anda Gómez'!I11+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J11" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!J11+'Julen Anda Gómez'!J11+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K11" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!K11+'Julen Anda Gómez'!K11+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L11" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!L11+'Julen Anda Gómez'!L11+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M11" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!M11+'Julen Anda Gómez'!M11+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N11" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!N11+'Julen Anda Gómez'!N11+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O11" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!O11+'Julen Anda Gómez'!O11+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="P11" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!P11+'Julen Anda Gómez'!P11+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Q11" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!Q11+'Julen Anda Gómez'!Q11+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="R11" s="18" t="e">
-        <f>'Cesar Manuel Llata Remacha'!R11+'Julen Anda Gómez'!R11+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="S11" s="5" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A12" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="5" t="e">
-        <f t="shared" ref="B12:R12" si="2">SUM(B2:B11)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C12" s="5" t="e">
-        <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="D12" s="5" t="e">
-        <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="E12" s="5" t="e">
-        <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="F12" s="5" t="e">
-        <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="G12" s="5" t="e">
-        <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="H12" s="5" t="e">
-        <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="I12" s="5" t="e">
-        <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="J12" s="5" t="e">
-        <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K12" s="5" t="e">
-        <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L12" s="5" t="e">
-        <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="M12" s="5" t="e">
-        <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="N12" s="5" t="e">
-        <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="O12" s="5" t="e">
-        <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="P12" s="5" t="e">
-        <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="Q12" s="5" t="e">
-        <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="R12" s="5" t="e">
-        <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="S12" s="5" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-    </row>
+      <c r="N2" s="27">
+        <v>0</v>
+      </c>
+      <c r="O2" s="27">
+        <v>0</v>
+      </c>
+      <c r="P2" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="27">
+        <v>0</v>
+      </c>
+      <c r="R2" s="27">
+        <v>0</v>
+      </c>
+      <c r="S2" s="28">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A3" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="27">
+        <v>0</v>
+      </c>
+      <c r="C3" s="27">
+        <v>0</v>
+      </c>
+      <c r="D3" s="27">
+        <v>0</v>
+      </c>
+      <c r="E3" s="27">
+        <v>5</v>
+      </c>
+      <c r="F3" s="27">
+        <v>5</v>
+      </c>
+      <c r="G3" s="27">
+        <v>10</v>
+      </c>
+      <c r="H3" s="27">
+        <v>8</v>
+      </c>
+      <c r="I3" s="27">
+        <v>0</v>
+      </c>
+      <c r="J3" s="27">
+        <v>0</v>
+      </c>
+      <c r="K3" s="27">
+        <v>0</v>
+      </c>
+      <c r="L3" s="27">
+        <v>2</v>
+      </c>
+      <c r="M3" s="27">
+        <v>0</v>
+      </c>
+      <c r="N3" s="27">
+        <v>0</v>
+      </c>
+      <c r="O3" s="27">
+        <v>0</v>
+      </c>
+      <c r="P3" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="27">
+        <v>0</v>
+      </c>
+      <c r="R3" s="27">
+        <v>0</v>
+      </c>
+      <c r="S3" s="28">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A4" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="27">
+        <v>0</v>
+      </c>
+      <c r="C4" s="27">
+        <v>0</v>
+      </c>
+      <c r="D4" s="27">
+        <v>0</v>
+      </c>
+      <c r="E4" s="27">
+        <v>0</v>
+      </c>
+      <c r="F4" s="27">
+        <v>0</v>
+      </c>
+      <c r="G4" s="27">
+        <v>8</v>
+      </c>
+      <c r="H4" s="27">
+        <v>9</v>
+      </c>
+      <c r="I4" s="27">
+        <v>0</v>
+      </c>
+      <c r="J4" s="27">
+        <v>0</v>
+      </c>
+      <c r="K4" s="27">
+        <v>5</v>
+      </c>
+      <c r="L4" s="27">
+        <v>0</v>
+      </c>
+      <c r="M4" s="27">
+        <v>0</v>
+      </c>
+      <c r="N4" s="27">
+        <v>0</v>
+      </c>
+      <c r="O4" s="27">
+        <v>0</v>
+      </c>
+      <c r="P4" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="27">
+        <v>0</v>
+      </c>
+      <c r="R4" s="27">
+        <v>0</v>
+      </c>
+      <c r="S4" s="28">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A5" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="27">
+        <v>0</v>
+      </c>
+      <c r="C5" s="27">
+        <v>0</v>
+      </c>
+      <c r="D5" s="27">
+        <v>0</v>
+      </c>
+      <c r="E5" s="27">
+        <v>0</v>
+      </c>
+      <c r="F5" s="27">
+        <v>0</v>
+      </c>
+      <c r="G5" s="27">
+        <v>0</v>
+      </c>
+      <c r="H5" s="27">
+        <v>10</v>
+      </c>
+      <c r="I5" s="27">
+        <v>0</v>
+      </c>
+      <c r="J5" s="27">
+        <v>0</v>
+      </c>
+      <c r="K5" s="27">
+        <v>0</v>
+      </c>
+      <c r="L5" s="27">
+        <v>0</v>
+      </c>
+      <c r="M5" s="27">
+        <v>0</v>
+      </c>
+      <c r="N5" s="27">
+        <v>0</v>
+      </c>
+      <c r="O5" s="27">
+        <v>0</v>
+      </c>
+      <c r="P5" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="27">
+        <v>0</v>
+      </c>
+      <c r="R5" s="27">
+        <v>0</v>
+      </c>
+      <c r="S5" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A6" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="27">
+        <v>0</v>
+      </c>
+      <c r="C6" s="27">
+        <v>0</v>
+      </c>
+      <c r="D6" s="27">
+        <v>0</v>
+      </c>
+      <c r="E6" s="27">
+        <v>2</v>
+      </c>
+      <c r="F6" s="27">
+        <v>2</v>
+      </c>
+      <c r="G6" s="27">
+        <v>2</v>
+      </c>
+      <c r="H6" s="27">
+        <v>5</v>
+      </c>
+      <c r="I6" s="27">
+        <v>5</v>
+      </c>
+      <c r="J6" s="27">
+        <v>20</v>
+      </c>
+      <c r="K6" s="27">
+        <v>10</v>
+      </c>
+      <c r="L6" s="27">
+        <v>10</v>
+      </c>
+      <c r="M6" s="27">
+        <v>0</v>
+      </c>
+      <c r="N6" s="27">
+        <v>0</v>
+      </c>
+      <c r="O6" s="27">
+        <v>2</v>
+      </c>
+      <c r="P6" s="27">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="27">
+        <v>5</v>
+      </c>
+      <c r="R6" s="27">
+        <v>0</v>
+      </c>
+      <c r="S6" s="28">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A7" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="27">
+        <v>0</v>
+      </c>
+      <c r="C7" s="27">
+        <v>0</v>
+      </c>
+      <c r="D7" s="27">
+        <v>0</v>
+      </c>
+      <c r="E7" s="27">
+        <v>0</v>
+      </c>
+      <c r="F7" s="27">
+        <v>0</v>
+      </c>
+      <c r="G7" s="27">
+        <v>0</v>
+      </c>
+      <c r="H7" s="27">
+        <v>0</v>
+      </c>
+      <c r="I7" s="27">
+        <v>0</v>
+      </c>
+      <c r="J7" s="27">
+        <v>5</v>
+      </c>
+      <c r="K7" s="27">
+        <v>5</v>
+      </c>
+      <c r="L7" s="27">
+        <v>5</v>
+      </c>
+      <c r="M7" s="27">
+        <v>5</v>
+      </c>
+      <c r="N7" s="27">
+        <v>5</v>
+      </c>
+      <c r="O7" s="27">
+        <v>5</v>
+      </c>
+      <c r="P7" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="27">
+        <v>0</v>
+      </c>
+      <c r="R7" s="27">
+        <v>0</v>
+      </c>
+      <c r="S7" s="28">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A8" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="27">
+        <v>0</v>
+      </c>
+      <c r="C8" s="27">
+        <v>0</v>
+      </c>
+      <c r="D8" s="27">
+        <v>0</v>
+      </c>
+      <c r="E8" s="27">
+        <v>0</v>
+      </c>
+      <c r="F8" s="27">
+        <v>0</v>
+      </c>
+      <c r="G8" s="27">
+        <v>0</v>
+      </c>
+      <c r="H8" s="27">
+        <v>0</v>
+      </c>
+      <c r="I8" s="27">
+        <v>0</v>
+      </c>
+      <c r="J8" s="27">
+        <v>0</v>
+      </c>
+      <c r="K8" s="27">
+        <v>0</v>
+      </c>
+      <c r="L8" s="27">
+        <v>0</v>
+      </c>
+      <c r="M8" s="27">
+        <v>0</v>
+      </c>
+      <c r="N8" s="27">
+        <v>0</v>
+      </c>
+      <c r="O8" s="27">
+        <v>0</v>
+      </c>
+      <c r="P8" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="27">
+        <v>0</v>
+      </c>
+      <c r="R8" s="27">
+        <v>0</v>
+      </c>
+      <c r="S8" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A9" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="27">
+        <v>0</v>
+      </c>
+      <c r="C9" s="27">
+        <v>0</v>
+      </c>
+      <c r="D9" s="27">
+        <v>0</v>
+      </c>
+      <c r="E9" s="27">
+        <v>0</v>
+      </c>
+      <c r="F9" s="27">
+        <v>0</v>
+      </c>
+      <c r="G9" s="27">
+        <v>0</v>
+      </c>
+      <c r="H9" s="27">
+        <v>0</v>
+      </c>
+      <c r="I9" s="27">
+        <v>0</v>
+      </c>
+      <c r="J9" s="27">
+        <v>0</v>
+      </c>
+      <c r="K9" s="27">
+        <v>0</v>
+      </c>
+      <c r="L9" s="27">
+        <v>0</v>
+      </c>
+      <c r="M9" s="27">
+        <v>0</v>
+      </c>
+      <c r="N9" s="27">
+        <v>3</v>
+      </c>
+      <c r="O9" s="27">
+        <v>4</v>
+      </c>
+      <c r="P9" s="27">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="27">
+        <v>0</v>
+      </c>
+      <c r="R9" s="27">
+        <v>0</v>
+      </c>
+      <c r="S9" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A10" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="27">
+        <v>0</v>
+      </c>
+      <c r="C10" s="27">
+        <v>0</v>
+      </c>
+      <c r="D10" s="27">
+        <v>0</v>
+      </c>
+      <c r="E10" s="27">
+        <v>0</v>
+      </c>
+      <c r="F10" s="27">
+        <v>0</v>
+      </c>
+      <c r="G10" s="27">
+        <v>0</v>
+      </c>
+      <c r="H10" s="27">
+        <v>0</v>
+      </c>
+      <c r="I10" s="27">
+        <v>0</v>
+      </c>
+      <c r="J10" s="27">
+        <v>0</v>
+      </c>
+      <c r="K10" s="27">
+        <v>0</v>
+      </c>
+      <c r="L10" s="27">
+        <v>10</v>
+      </c>
+      <c r="M10" s="27">
+        <v>0</v>
+      </c>
+      <c r="N10" s="27">
+        <v>1</v>
+      </c>
+      <c r="O10" s="27">
+        <v>2</v>
+      </c>
+      <c r="P10" s="27">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="27">
+        <v>0</v>
+      </c>
+      <c r="R10" s="27">
+        <v>0</v>
+      </c>
+      <c r="S10" s="28">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A11" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="27">
+        <v>0</v>
+      </c>
+      <c r="C11" s="27">
+        <v>0</v>
+      </c>
+      <c r="D11" s="27">
+        <v>0</v>
+      </c>
+      <c r="E11" s="27">
+        <v>0</v>
+      </c>
+      <c r="F11" s="27">
+        <v>0</v>
+      </c>
+      <c r="G11" s="27">
+        <v>0</v>
+      </c>
+      <c r="H11" s="27">
+        <v>0</v>
+      </c>
+      <c r="I11" s="27">
+        <v>16</v>
+      </c>
+      <c r="J11" s="27">
+        <v>0</v>
+      </c>
+      <c r="K11" s="27">
+        <v>0</v>
+      </c>
+      <c r="L11" s="27">
+        <v>6</v>
+      </c>
+      <c r="M11" s="27">
+        <v>0</v>
+      </c>
+      <c r="N11" s="27">
+        <v>2</v>
+      </c>
+      <c r="O11" s="27">
+        <v>4</v>
+      </c>
+      <c r="P11" s="27">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="27">
+        <v>1</v>
+      </c>
+      <c r="R11" s="27">
+        <v>0</v>
+      </c>
+      <c r="S11" s="28">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="15.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -27034,7 +26817,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="4">
@@ -27110,7 +26893,7 @@
       </c>
     </row>
     <row r="2" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A2" s="21" t="str">
+      <c r="A2" s="20" t="str">
         <f>Gantt!A3</f>
         <v>T1</v>
       </c>
@@ -27153,7 +26936,7 @@
       </c>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A3" s="21" t="str">
+      <c r="A3" s="20" t="str">
         <f>Gantt!A4</f>
         <v>T2</v>
       </c>
@@ -27190,7 +26973,7 @@
       </c>
     </row>
     <row r="4" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A4" s="21" t="str">
+      <c r="A4" s="20" t="str">
         <f>Gantt!A5</f>
         <v>T3</v>
       </c>
@@ -27223,7 +27006,7 @@
       </c>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A5" s="21" t="str">
+      <c r="A5" s="20" t="str">
         <f>Gantt!A6</f>
         <v>T4</v>
       </c>
@@ -27252,7 +27035,7 @@
       </c>
     </row>
     <row r="6" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A6" s="21" t="str">
+      <c r="A6" s="20" t="str">
         <f>Gantt!A7</f>
         <v>T5</v>
       </c>
@@ -27281,7 +27064,7 @@
       </c>
     </row>
     <row r="7" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A7" s="21" t="str">
+      <c r="A7" s="20" t="str">
         <f>Gantt!A8</f>
         <v>T6</v>
       </c>
@@ -27320,7 +27103,7 @@
       </c>
     </row>
     <row r="8" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A8" s="21" t="str">
+      <c r="A8" s="20" t="str">
         <f>Gantt!A9</f>
         <v>T7</v>
       </c>
@@ -27347,7 +27130,7 @@
       </c>
     </row>
     <row r="9" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A9" s="21" t="str">
+      <c r="A9" s="20" t="str">
         <f>Gantt!A10</f>
         <v>T8</v>
       </c>
@@ -27380,7 +27163,7 @@
       </c>
     </row>
     <row r="10" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A10" s="21" t="str">
+      <c r="A10" s="20" t="str">
         <f>Gantt!A11</f>
         <v>T9</v>
       </c>
@@ -27409,7 +27192,7 @@
       </c>
     </row>
     <row r="11" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A11" s="21" t="str">
+      <c r="A11" s="20" t="str">
         <f>Gantt!A12</f>
         <v>T10</v>
       </c>
@@ -27444,7 +27227,7 @@
       </c>
     </row>
     <row r="12" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="5">
@@ -27539,7 +27322,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="4">
@@ -27615,7 +27398,7 @@
       </c>
     </row>
     <row r="2" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A2" s="21" t="str">
+      <c r="A2" s="20" t="str">
         <f>Gantt!A3</f>
         <v>T1</v>
       </c>
@@ -27658,7 +27441,7 @@
       </c>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A3" s="21" t="str">
+      <c r="A3" s="20" t="str">
         <f>Gantt!A4</f>
         <v>T2</v>
       </c>
@@ -27689,7 +27472,7 @@
       </c>
     </row>
     <row r="4" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A4" s="21" t="str">
+      <c r="A4" s="20" t="str">
         <f>Gantt!A5</f>
         <v>T3</v>
       </c>
@@ -27720,7 +27503,7 @@
       </c>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A5" s="21" t="str">
+      <c r="A5" s="20" t="str">
         <f>Gantt!A6</f>
         <v>T4</v>
       </c>
@@ -27749,7 +27532,7 @@
       </c>
     </row>
     <row r="6" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A6" s="21" t="str">
+      <c r="A6" s="20" t="str">
         <f>Gantt!A7</f>
         <v>T5</v>
       </c>
@@ -27798,7 +27581,7 @@
       </c>
     </row>
     <row r="7" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A7" s="21" t="str">
+      <c r="A7" s="20" t="str">
         <f>Gantt!A8</f>
         <v>T6</v>
       </c>
@@ -27825,7 +27608,7 @@
       </c>
     </row>
     <row r="8" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A8" s="21" t="str">
+      <c r="A8" s="20" t="str">
         <f>Gantt!A9</f>
         <v>T7</v>
       </c>
@@ -27852,7 +27635,7 @@
       </c>
     </row>
     <row r="9" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A9" s="21" t="str">
+      <c r="A9" s="20" t="str">
         <f>Gantt!A10</f>
         <v>T8</v>
       </c>
@@ -27885,7 +27668,7 @@
       </c>
     </row>
     <row r="10" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A10" s="21" t="str">
+      <c r="A10" s="20" t="str">
         <f>Gantt!A11</f>
         <v>T9</v>
       </c>
@@ -27920,7 +27703,7 @@
       </c>
     </row>
     <row r="11" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A11" s="21" t="str">
+      <c r="A11" s="20" t="str">
         <f>Gantt!A12</f>
         <v>T10</v>
       </c>
@@ -27957,7 +27740,7 @@
       </c>
     </row>
     <row r="12" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="5">
